--- a/4학년피구대회일정.xlsx
+++ b/4학년피구대회일정.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\2026\학년협의\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56262B6E-4F77-4D14-AC06-8DF36BDE96CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B9403C-0192-4F07-80F6-1A3C717B1369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DD21F046-BAC6-4B5D-AC41-BB8291C46378}"/>
+    <workbookView xWindow="420" yWindow="0" windowWidth="28215" windowHeight="15480" xr2:uid="{DD21F046-BAC6-4B5D-AC41-BB8291C46378}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="72">
   <si>
     <t>구분</t>
   </si>
@@ -43,10 +43,6 @@
   </si>
   <si>
     <t>금</t>
-  </si>
-  <si>
-    <t>담임</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <r>
@@ -242,231 +238,801 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>교실체육1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>:</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>목</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>금</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1주</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2주</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>3주</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>A1:A2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>A3:A4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>A5:A6</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>A1:A3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>A</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>A7:A1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>A2:A3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>A:4:A5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>A:6:A7</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>A2:A4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>A5:A7</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>A6:A1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>A2:A5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>A3:A7</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>A3:A6</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>A2:A7</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>A1:A5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>A4:A6</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>A3:A5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>4주</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>A2:A6</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>A4:A7</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>A1:A4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>B1:B2</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>B3:B4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>B5:B6</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>B7:B1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>B2:B3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>B4:B5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>B6:B7</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>B1:B3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>B2:B4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>B5:B7</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>B6:B1</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>B2:B5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>B3:B6</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>B4:B7</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>B1:B5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>B2:B6</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>B3:B7</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>B4:B6</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>B1:B4</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>B3:B5</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>B2:B7</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>A1위:B1위</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>A2위:B2위</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>B</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>담임심판</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>요일별 경기 횟수</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>A4:A5</t>
+    <t>한승종</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3반:4반</t>
+  </si>
+  <si>
+    <t>2반:5반</t>
+  </si>
+  <si>
+    <t>9반:8반</t>
+  </si>
+  <si>
+    <t>12반:6반</t>
+  </si>
+  <si>
+    <t>8반:1반</t>
+  </si>
+  <si>
+    <t>11반:4반</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>교실체육1대신</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3반:11반</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10반:7반</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>9반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:14반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>7반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:2반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>12반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:8반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:5반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:13반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>6반:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>8반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:6반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>7반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:3반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>9반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:12반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>6반:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>13반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:5반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>6반:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>9반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>7반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:4반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>14반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:1반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>12반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:13반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>7반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:11반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>14반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:13반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2위:2위</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1위:1위</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>13반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:9반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>14반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:12반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:10반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이순희</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>11반:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:12반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10반:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>11반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:7반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>8반:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>13반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2반:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>11반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:9반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>14반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:6반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:4반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:10반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>14반:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>8반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2반:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>심판명</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>횟수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>3반:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10반</t>
+    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -477,7 +1043,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="m\-d"/>
   </numFmts>
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -558,14 +1124,6 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color theme="6"/>
-      <name val="맑은 고딕"/>
-      <family val="2"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
       <color rgb="FF7030A0"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -614,8 +1172,63 @@
       <family val="2"/>
       <charset val="129"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF7030A0"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFC00000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="9" tint="-0.249977111117893"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="9" tint="-0.249977111117893"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="14">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -670,30 +1283,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="19">
     <border>
@@ -957,38 +1546,32 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1009,7 +1592,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1018,13 +1601,13 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1033,10 +1616,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1045,61 +1625,67 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="15" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="14" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="15" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="16" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1117,10 +1703,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1129,11 +1718,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1150,14 +1739,23 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1473,78 +2071,80 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F15F584-BA2D-44A2-BB90-81E8A9F90C1A}">
-  <dimension ref="A1:AH25"/>
+  <dimension ref="A1:AH30"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="9" style="6"/>
-    <col min="2" max="2" width="7.875" style="6" customWidth="1"/>
-    <col min="3" max="3" width="7" style="6" customWidth="1"/>
-    <col min="4" max="4" width="7.125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="7.25" style="6" customWidth="1"/>
-    <col min="6" max="8" width="7.125" style="6" customWidth="1"/>
-    <col min="9" max="9" width="2.5" style="6" customWidth="1"/>
-    <col min="10" max="10" width="9" style="6"/>
-    <col min="11" max="11" width="7.875" style="6" customWidth="1"/>
-    <col min="12" max="12" width="7.25" style="6" customWidth="1"/>
-    <col min="13" max="13" width="7.625" style="6" customWidth="1"/>
-    <col min="14" max="14" width="8" style="6" customWidth="1"/>
-    <col min="15" max="15" width="3.375" style="6" customWidth="1"/>
-    <col min="16" max="16" width="7.625" style="6" customWidth="1"/>
-    <col min="17" max="17" width="7.875" style="6" customWidth="1"/>
-    <col min="18" max="18" width="2.625" style="6" customWidth="1"/>
-    <col min="19" max="19" width="9" style="6"/>
-    <col min="20" max="20" width="6.875" style="6" customWidth="1"/>
-    <col min="21" max="21" width="7.375" style="6" customWidth="1"/>
-    <col min="22" max="22" width="7.25" style="6" customWidth="1"/>
-    <col min="23" max="23" width="8.125" style="6" customWidth="1"/>
-    <col min="24" max="24" width="4.25" style="6" customWidth="1"/>
-    <col min="25" max="25" width="9" style="6"/>
-    <col min="26" max="26" width="2.875" style="6" customWidth="1"/>
-    <col min="27" max="27" width="9" style="6"/>
-    <col min="28" max="28" width="7.875" style="6" customWidth="1"/>
-    <col min="29" max="29" width="7.625" style="6" customWidth="1"/>
-    <col min="30" max="30" width="10.25" style="6" customWidth="1"/>
-    <col min="31" max="31" width="9" style="6"/>
-    <col min="32" max="32" width="5.375" style="6" customWidth="1"/>
-    <col min="33" max="33" width="6.75" style="6" customWidth="1"/>
-    <col min="34" max="16384" width="9" style="6"/>
+    <col min="1" max="1" width="9" style="4"/>
+    <col min="2" max="2" width="7.875" style="4" customWidth="1"/>
+    <col min="3" max="3" width="8.125" style="4" customWidth="1"/>
+    <col min="4" max="4" width="8.625" style="4" customWidth="1"/>
+    <col min="5" max="5" width="8.375" style="4" customWidth="1"/>
+    <col min="6" max="6" width="8.5" style="4" customWidth="1"/>
+    <col min="7" max="7" width="9.125" style="4" customWidth="1"/>
+    <col min="8" max="8" width="8" style="4" customWidth="1"/>
+    <col min="9" max="9" width="2.5" style="4" customWidth="1"/>
+    <col min="10" max="10" width="9" style="4"/>
+    <col min="11" max="11" width="7.875" style="4" customWidth="1"/>
+    <col min="12" max="12" width="7.25" style="4" customWidth="1"/>
+    <col min="13" max="13" width="7.625" style="4" customWidth="1"/>
+    <col min="14" max="14" width="8" style="4" customWidth="1"/>
+    <col min="15" max="15" width="3.375" style="4" customWidth="1"/>
+    <col min="16" max="16" width="8.75" style="4" customWidth="1"/>
+    <col min="17" max="17" width="9" style="4" customWidth="1"/>
+    <col min="18" max="18" width="2.625" style="4" customWidth="1"/>
+    <col min="19" max="19" width="9" style="4"/>
+    <col min="20" max="20" width="7.75" style="4" customWidth="1"/>
+    <col min="21" max="21" width="7.875" style="4" customWidth="1"/>
+    <col min="22" max="22" width="8.875" style="4" customWidth="1"/>
+    <col min="23" max="23" width="8.125" style="4" customWidth="1"/>
+    <col min="24" max="24" width="4.25" style="4" customWidth="1"/>
+    <col min="25" max="25" width="9" style="4"/>
+    <col min="26" max="26" width="2.875" style="4" customWidth="1"/>
+    <col min="27" max="27" width="9" style="4"/>
+    <col min="28" max="28" width="7.875" style="4" customWidth="1"/>
+    <col min="29" max="29" width="7.625" style="4" customWidth="1"/>
+    <col min="30" max="30" width="10.25" style="4" customWidth="1"/>
+    <col min="31" max="31" width="9" style="4"/>
+    <col min="32" max="32" width="5.375" style="4" customWidth="1"/>
+    <col min="33" max="33" width="6.75" style="4" customWidth="1"/>
+    <col min="34" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="59" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B1" s="59"/>
       <c r="C1" s="59"/>
-      <c r="D1" s="11"/>
+      <c r="D1" s="9"/>
       <c r="J1" s="59" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K1" s="59"/>
       <c r="L1" s="59"/>
       <c r="S1" s="59" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="T1" s="59"/>
       <c r="U1" s="59"/>
-      <c r="Z1" s="14"/>
+      <c r="Z1" s="12"/>
       <c r="AA1" s="59" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AB1" s="59"/>
       <c r="AC1" s="59"/>
-      <c r="AD1" s="11"/>
+      <c r="AD1" s="9"/>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.2">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="53" t="s">
+      <c r="B2" s="57" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="58"/>
+      <c r="D2" s="21" t="s">
         <v>9</v>
-      </c>
-      <c r="C2" s="54"/>
-      <c r="D2" s="23" t="s">
-        <v>10</v>
       </c>
       <c r="E2" s="60" t="s">
         <v>1</v>
@@ -1553,16 +2153,16 @@
       <c r="G2" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="65"/>
-      <c r="J2" s="19" t="s">
+      <c r="H2" s="64"/>
+      <c r="J2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="K2" s="53" t="s">
+      <c r="K2" s="57" t="s">
+        <v>8</v>
+      </c>
+      <c r="L2" s="58"/>
+      <c r="M2" s="18" t="s">
         <v>9</v>
-      </c>
-      <c r="L2" s="54"/>
-      <c r="M2" s="20" t="s">
-        <v>10</v>
       </c>
       <c r="N2" s="60" t="s">
         <v>1</v>
@@ -1571,900 +2171,987 @@
       <c r="P2" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="Q2" s="65"/>
-      <c r="S2" s="19" t="s">
+      <c r="Q2" s="64"/>
+      <c r="S2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="T2" s="53" t="s">
+      <c r="T2" s="57" t="s">
+        <v>8</v>
+      </c>
+      <c r="U2" s="58"/>
+      <c r="V2" s="18" t="s">
         <v>9</v>
-      </c>
-      <c r="U2" s="54"/>
-      <c r="V2" s="20" t="s">
-        <v>10</v>
       </c>
       <c r="W2" s="60" t="s">
         <v>1</v>
       </c>
       <c r="X2" s="61"/>
-      <c r="Y2" s="30" t="s">
+      <c r="Y2" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="Z2" s="15"/>
-      <c r="AA2" s="19" t="s">
+      <c r="Z2" s="13"/>
+      <c r="AA2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="AB2" s="53" t="s">
+      <c r="AB2" s="57" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC2" s="58"/>
+      <c r="AD2" s="21" t="s">
         <v>9</v>
-      </c>
-      <c r="AC2" s="54"/>
-      <c r="AD2" s="23" t="s">
-        <v>10</v>
       </c>
       <c r="AE2" s="60" t="s">
         <v>1</v>
       </c>
       <c r="AF2" s="61"/>
-      <c r="AG2" s="31" t="s">
+      <c r="AG2" s="27" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:34" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="55" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="51"/>
-      <c r="D3" s="51"/>
-      <c r="E3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="50"/>
+      <c r="C3" s="50"/>
+      <c r="D3" s="50"/>
+      <c r="E3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="51"/>
+      <c r="J3" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="K3" s="50"/>
+      <c r="L3" s="50"/>
+      <c r="M3" s="54"/>
+      <c r="N3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="O3" s="50"/>
+      <c r="P3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q3" s="51"/>
+      <c r="S3" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="T3" s="50"/>
+      <c r="U3" s="50"/>
+      <c r="V3" s="62"/>
+      <c r="W3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="X3" s="50"/>
+      <c r="Y3" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="Z3" s="14"/>
+      <c r="AA3" s="55" t="s">
+        <v>4</v>
+      </c>
+      <c r="AB3" s="50"/>
+      <c r="AC3" s="50"/>
+      <c r="AD3" s="50"/>
+      <c r="AE3" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="52"/>
-      <c r="J3" s="55" t="s">
-        <v>5</v>
-      </c>
-      <c r="K3" s="51"/>
-      <c r="L3" s="51"/>
-      <c r="M3" s="64"/>
-      <c r="N3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="O3" s="51"/>
-      <c r="P3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q3" s="52"/>
-      <c r="S3" s="55" t="s">
-        <v>5</v>
-      </c>
-      <c r="T3" s="51"/>
-      <c r="U3" s="51"/>
-      <c r="V3" s="62"/>
-      <c r="W3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="X3" s="51"/>
-      <c r="Y3" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z3" s="16"/>
-      <c r="AA3" s="55" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB3" s="51"/>
-      <c r="AC3" s="51"/>
-      <c r="AD3" s="51"/>
-      <c r="AE3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="AF3" s="51"/>
-      <c r="AG3" s="7" t="s">
-        <v>21</v>
+      <c r="AF3" s="50"/>
+      <c r="AG3" s="5" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:34" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="56"/>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
-      <c r="E4" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="F4" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="G4" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="H4" s="52"/>
+      <c r="B4" s="50"/>
+      <c r="C4" s="50"/>
+      <c r="D4" s="50"/>
+      <c r="E4" s="42" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="42" t="s">
+        <v>36</v>
+      </c>
+      <c r="G4" s="43" t="s">
+        <v>52</v>
+      </c>
+      <c r="H4" s="51"/>
       <c r="J4" s="56"/>
-      <c r="K4" s="51"/>
-      <c r="L4" s="51"/>
-      <c r="M4" s="64"/>
-      <c r="N4" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="O4" s="51"/>
-      <c r="P4" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="Q4" s="52"/>
+      <c r="K4" s="50"/>
+      <c r="L4" s="50"/>
+      <c r="M4" s="54"/>
+      <c r="N4" s="42" t="s">
+        <v>55</v>
+      </c>
+      <c r="O4" s="50"/>
+      <c r="P4" s="43" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q4" s="51"/>
       <c r="S4" s="56"/>
-      <c r="T4" s="51"/>
-      <c r="U4" s="51"/>
+      <c r="T4" s="50"/>
+      <c r="U4" s="50"/>
       <c r="V4" s="63"/>
-      <c r="W4" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="X4" s="51"/>
-      <c r="Y4" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="Z4" s="16"/>
+      <c r="W4" s="43" t="s">
+        <v>47</v>
+      </c>
+      <c r="X4" s="50"/>
+      <c r="Y4" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="Z4" s="14"/>
       <c r="AA4" s="56"/>
-      <c r="AB4" s="51"/>
-      <c r="AC4" s="51"/>
-      <c r="AD4" s="51"/>
-      <c r="AE4" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF4" s="51"/>
-      <c r="AG4" s="8"/>
+      <c r="AB4" s="50"/>
+      <c r="AC4" s="50"/>
+      <c r="AD4" s="50"/>
+      <c r="AE4" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="AF4" s="50"/>
+      <c r="AG4" s="6"/>
     </row>
     <row r="5" spans="1:34" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="55" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
-      <c r="E5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="H5" s="52"/>
+        <v>5</v>
+      </c>
+      <c r="B5" s="50"/>
+      <c r="C5" s="50"/>
+      <c r="D5" s="50"/>
+      <c r="E5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H5" s="51"/>
       <c r="J5" s="55" t="s">
-        <v>6</v>
-      </c>
-      <c r="K5" s="51"/>
-      <c r="L5" s="51"/>
-      <c r="M5" s="64"/>
-      <c r="N5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="O5" s="51"/>
-      <c r="P5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q5" s="52"/>
+        <v>5</v>
+      </c>
+      <c r="K5" s="50"/>
+      <c r="L5" s="50"/>
+      <c r="M5" s="54"/>
+      <c r="N5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="O5" s="50"/>
+      <c r="P5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q5" s="51"/>
       <c r="S5" s="55" t="s">
-        <v>6</v>
-      </c>
-      <c r="T5" s="51"/>
-      <c r="U5" s="51"/>
+        <v>5</v>
+      </c>
+      <c r="T5" s="50"/>
+      <c r="U5" s="50"/>
       <c r="V5" s="62"/>
       <c r="W5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="X5" s="51"/>
-      <c r="Y5" s="9"/>
-      <c r="Z5" s="16"/>
+        <v>23</v>
+      </c>
+      <c r="X5" s="50"/>
+      <c r="Y5" s="7"/>
+      <c r="Z5" s="14"/>
       <c r="AA5" s="55" t="s">
-        <v>6</v>
-      </c>
-      <c r="AB5" s="51"/>
-      <c r="AC5" s="51"/>
-      <c r="AD5" s="51"/>
-      <c r="AE5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="AF5" s="51"/>
-      <c r="AG5" s="7"/>
+        <v>5</v>
+      </c>
+      <c r="AB5" s="50"/>
+      <c r="AC5" s="50"/>
+      <c r="AD5" s="50"/>
+      <c r="AE5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="AF5" s="50"/>
+      <c r="AG5" s="5"/>
     </row>
     <row r="6" spans="1:34" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="56"/>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="F6" s="13" t="s">
+      <c r="B6" s="50"/>
+      <c r="C6" s="50"/>
+      <c r="D6" s="50"/>
+      <c r="E6" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="F6" s="43" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="46" t="s">
+        <v>53</v>
+      </c>
+      <c r="H6" s="51"/>
+      <c r="J6" s="56"/>
+      <c r="K6" s="50"/>
+      <c r="L6" s="50"/>
+      <c r="M6" s="54"/>
+      <c r="N6" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="O6" s="50"/>
+      <c r="P6" s="43" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q6" s="51"/>
+      <c r="S6" s="56"/>
+      <c r="T6" s="50"/>
+      <c r="U6" s="50"/>
+      <c r="V6" s="63"/>
+      <c r="W6" s="43" t="s">
         <v>57</v>
       </c>
-      <c r="G6" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" s="52"/>
-      <c r="J6" s="56"/>
-      <c r="K6" s="51"/>
-      <c r="L6" s="51"/>
-      <c r="M6" s="64"/>
-      <c r="N6" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="O6" s="51"/>
-      <c r="P6" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q6" s="52"/>
-      <c r="S6" s="56"/>
-      <c r="T6" s="51"/>
-      <c r="U6" s="51"/>
-      <c r="V6" s="63"/>
-      <c r="W6" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="X6" s="51"/>
-      <c r="Y6" s="10"/>
-      <c r="Z6" s="16"/>
+      <c r="X6" s="50"/>
+      <c r="Y6" s="8"/>
+      <c r="Z6" s="14"/>
       <c r="AA6" s="56"/>
-      <c r="AB6" s="51"/>
-      <c r="AC6" s="51"/>
-      <c r="AD6" s="51"/>
-      <c r="AE6" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="AF6" s="51"/>
-      <c r="AG6" s="8"/>
+      <c r="AB6" s="50"/>
+      <c r="AC6" s="50"/>
+      <c r="AD6" s="50"/>
+      <c r="AE6" s="43" t="s">
+        <v>49</v>
+      </c>
+      <c r="AF6" s="50"/>
+      <c r="AG6" s="6"/>
     </row>
     <row r="7" spans="1:34" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="55" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="51"/>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F7" s="49"/>
-      <c r="G7" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="50"/>
+      <c r="C7" s="50"/>
+      <c r="D7" s="50"/>
+      <c r="E7" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="F7" s="48"/>
+      <c r="G7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="26" t="s">
-        <v>14</v>
-      </c>
       <c r="J7" s="55" t="s">
-        <v>7</v>
-      </c>
-      <c r="K7" s="51"/>
-      <c r="L7" s="51"/>
-      <c r="M7" s="64"/>
-      <c r="N7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="K7" s="50"/>
+      <c r="L7" s="50"/>
+      <c r="M7" s="54"/>
+      <c r="N7" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="O7" s="50"/>
+      <c r="P7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q7" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="S7" s="55" t="s">
+        <v>6</v>
+      </c>
+      <c r="T7" s="50"/>
+      <c r="U7" s="50"/>
+      <c r="V7" s="62"/>
+      <c r="W7" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="X7" s="50"/>
+      <c r="Y7" s="7"/>
+      <c r="Z7" s="15"/>
+      <c r="AA7" s="55" t="s">
+        <v>6</v>
+      </c>
+      <c r="AB7" s="50"/>
+      <c r="AC7" s="50"/>
+      <c r="AD7" s="50"/>
+      <c r="AE7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="O7" s="51"/>
-      <c r="P7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q7" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="S7" s="55" t="s">
-        <v>7</v>
-      </c>
-      <c r="T7" s="51"/>
-      <c r="U7" s="51"/>
-      <c r="V7" s="62"/>
-      <c r="W7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="X7" s="51"/>
-      <c r="Y7" s="9"/>
-      <c r="Z7" s="17"/>
-      <c r="AA7" s="55" t="s">
-        <v>7</v>
-      </c>
-      <c r="AB7" s="51"/>
-      <c r="AC7" s="51"/>
-      <c r="AD7" s="51"/>
-      <c r="AE7" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="AF7" s="51"/>
-      <c r="AG7" s="7"/>
+      <c r="AF7" s="50"/>
+      <c r="AG7" s="5"/>
     </row>
     <row r="8" spans="1:34" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="56"/>
-      <c r="B8" s="51"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
-      <c r="E8" s="48" t="s">
-        <v>23</v>
-      </c>
-      <c r="F8" s="49"/>
-      <c r="G8" s="33" t="s">
-        <v>55</v>
-      </c>
-      <c r="H8" s="27" t="s">
-        <v>79</v>
+      <c r="B8" s="50"/>
+      <c r="C8" s="50"/>
+      <c r="D8" s="50"/>
+      <c r="E8" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="48"/>
+      <c r="G8" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="H8" s="24" t="s">
+        <v>29</v>
       </c>
       <c r="J8" s="56"/>
-      <c r="K8" s="51"/>
-      <c r="L8" s="51"/>
-      <c r="M8" s="64"/>
-      <c r="N8" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="O8" s="51"/>
-      <c r="P8" s="13" t="s">
+      <c r="K8" s="50"/>
+      <c r="L8" s="50"/>
+      <c r="M8" s="54"/>
+      <c r="N8" s="42" t="s">
+        <v>60</v>
+      </c>
+      <c r="O8" s="50"/>
+      <c r="P8" s="43" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q8" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="Q8" s="27" t="s">
-        <v>51</v>
-      </c>
       <c r="S8" s="56"/>
-      <c r="T8" s="51"/>
-      <c r="U8" s="51"/>
+      <c r="T8" s="50"/>
+      <c r="U8" s="50"/>
       <c r="V8" s="63"/>
-      <c r="W8" s="6" t="s">
-        <v>71</v>
-      </c>
-      <c r="X8" s="51"/>
-      <c r="Y8" s="10"/>
-      <c r="Z8" s="18"/>
+      <c r="W8" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="X8" s="50"/>
+      <c r="Y8" s="8"/>
+      <c r="Z8" s="16"/>
       <c r="AA8" s="56"/>
-      <c r="AB8" s="51"/>
-      <c r="AC8" s="51"/>
-      <c r="AD8" s="51"/>
-      <c r="AE8" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="AF8" s="51"/>
-      <c r="AG8" s="8"/>
+      <c r="AB8" s="50"/>
+      <c r="AC8" s="50"/>
+      <c r="AD8" s="50"/>
+      <c r="AE8" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF8" s="50"/>
+      <c r="AG8" s="6"/>
     </row>
     <row r="9" spans="1:34" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="55" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="51"/>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
-      <c r="E9" s="48" t="s">
-        <v>22</v>
-      </c>
-      <c r="F9" s="49"/>
-      <c r="G9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="50"/>
+      <c r="C9" s="50"/>
+      <c r="D9" s="50"/>
+      <c r="E9" s="47" t="s">
+        <v>21</v>
+      </c>
+      <c r="F9" s="48"/>
+      <c r="G9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="H9" s="26" t="s">
-        <v>14</v>
-      </c>
       <c r="J9" s="55" t="s">
-        <v>8</v>
-      </c>
-      <c r="K9" s="51"/>
-      <c r="L9" s="51"/>
-      <c r="M9" s="64"/>
-      <c r="N9" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="O9" s="51"/>
-      <c r="P9" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="K9" s="50"/>
+      <c r="L9" s="50"/>
+      <c r="M9" s="54"/>
+      <c r="N9" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="Q9" s="26" t="s">
-        <v>14</v>
+      <c r="O9" s="50"/>
+      <c r="P9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q9" s="67" t="s">
+        <v>10</v>
       </c>
       <c r="S9" s="55" t="s">
-        <v>8</v>
-      </c>
-      <c r="T9" s="51"/>
-      <c r="U9" s="51"/>
+        <v>7</v>
+      </c>
+      <c r="T9" s="50"/>
+      <c r="U9" s="50"/>
       <c r="V9" s="62"/>
-      <c r="W9" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="X9" s="51"/>
-      <c r="Y9" s="9"/>
-      <c r="Z9" s="17"/>
+      <c r="W9" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="X9" s="50"/>
+      <c r="Y9" s="7"/>
+      <c r="Z9" s="15"/>
       <c r="AA9" s="55" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB9" s="51"/>
-      <c r="AC9" s="51"/>
-      <c r="AD9" s="51"/>
-      <c r="AE9" s="45" t="s">
-        <v>13</v>
-      </c>
-      <c r="AF9" s="51"/>
-      <c r="AG9" s="7"/>
+        <v>7</v>
+      </c>
+      <c r="AB9" s="50"/>
+      <c r="AC9" s="50"/>
+      <c r="AD9" s="50"/>
+      <c r="AE9" s="33" t="s">
+        <v>12</v>
+      </c>
+      <c r="AF9" s="50"/>
+      <c r="AG9" s="5"/>
     </row>
     <row r="10" spans="1:34" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="56"/>
-      <c r="B10" s="51"/>
-      <c r="C10" s="51"/>
-      <c r="D10" s="51"/>
-      <c r="E10" s="50"/>
-      <c r="F10" s="49"/>
-      <c r="G10" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="H10" s="27" t="s">
+      <c r="B10" s="50"/>
+      <c r="C10" s="50"/>
+      <c r="D10" s="50"/>
+      <c r="E10" s="49"/>
+      <c r="F10" s="48"/>
+      <c r="G10" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="H10" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="J10" s="56"/>
+      <c r="K10" s="50"/>
+      <c r="L10" s="50"/>
+      <c r="M10" s="54"/>
+      <c r="N10" s="42" t="s">
+        <v>67</v>
+      </c>
+      <c r="O10" s="50"/>
+      <c r="P10" s="43" t="s">
         <v>58</v>
       </c>
-      <c r="J10" s="56"/>
-      <c r="K10" s="51"/>
-      <c r="L10" s="51"/>
-      <c r="M10" s="64"/>
-      <c r="N10" s="12" t="s">
+      <c r="Q10" s="45" t="s">
         <v>61</v>
       </c>
-      <c r="O10" s="51"/>
-      <c r="P10" s="13" t="s">
-        <v>63</v>
-      </c>
-      <c r="Q10" s="35" t="s">
-        <v>66</v>
-      </c>
       <c r="S10" s="56"/>
-      <c r="T10" s="51"/>
-      <c r="U10" s="51"/>
+      <c r="T10" s="50"/>
+      <c r="U10" s="50"/>
       <c r="V10" s="63"/>
-      <c r="W10" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="X10" s="51"/>
-      <c r="Y10" s="10"/>
-      <c r="Z10" s="18"/>
+      <c r="W10" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="X10" s="50"/>
+      <c r="Y10" s="8"/>
+      <c r="Z10" s="16"/>
       <c r="AA10" s="56"/>
-      <c r="AB10" s="51"/>
-      <c r="AC10" s="51"/>
-      <c r="AD10" s="51"/>
-      <c r="AE10" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="AF10" s="51"/>
-      <c r="AG10" s="8"/>
+      <c r="AB10" s="50"/>
+      <c r="AC10" s="50"/>
+      <c r="AD10" s="50"/>
+      <c r="AE10" s="11" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF10" s="50"/>
+      <c r="AG10" s="6"/>
     </row>
     <row r="11" spans="1:34" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="66" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="A11" s="65" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="29"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H11" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="J11" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="E11" s="36"/>
-      <c r="F11" s="37"/>
-      <c r="G11" s="3" t="s">
+      <c r="K11" s="37" t="s">
+        <v>10</v>
+      </c>
+      <c r="L11" s="39" t="s">
+        <v>56</v>
+      </c>
+      <c r="M11" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="J11" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="K11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="L11" s="1" t="s">
+      <c r="N11" s="29"/>
+      <c r="O11" s="30"/>
+      <c r="P11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="Q11" s="40" t="s">
+        <v>13</v>
+      </c>
+      <c r="S11" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="M11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="N11" s="36"/>
-      <c r="O11" s="37"/>
-      <c r="P11" s="3" t="s">
+      <c r="T11" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="Q11" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="S11" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="T11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="U11" s="1" t="s">
+      <c r="U11" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="V11" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="W11" s="29"/>
+      <c r="X11" s="30"/>
+      <c r="Y11" s="7"/>
+      <c r="Z11" s="15"/>
+      <c r="AA11" s="52" t="s">
         <v>3</v>
       </c>
-      <c r="V11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="W11" s="36"/>
-      <c r="X11" s="37"/>
-      <c r="Y11" s="9"/>
-      <c r="Z11" s="17"/>
-      <c r="AA11" s="57" t="s">
-        <v>4</v>
-      </c>
-      <c r="AB11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AC11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="AD11" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="AE11" s="36"/>
-      <c r="AF11" s="37"/>
-      <c r="AG11" s="7"/>
+      <c r="AB11" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="AC11" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="AD11" s="39" t="s">
+        <v>13</v>
+      </c>
+      <c r="AE11" s="29"/>
+      <c r="AF11" s="30"/>
+      <c r="AG11" s="5"/>
     </row>
     <row r="12" spans="1:34" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="58"/>
-      <c r="B12" s="21" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="21" t="s">
-        <v>30</v>
-      </c>
-      <c r="D12" s="28" t="s">
+      <c r="A12" s="53"/>
+      <c r="B12" s="41" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="25" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="38"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="21" t="s">
+      <c r="E12" s="31"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="41" t="s">
+        <v>66</v>
+      </c>
+      <c r="H12" s="44" t="s">
+        <v>40</v>
+      </c>
+      <c r="J12" s="53"/>
+      <c r="K12" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="L12" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="M12" s="41" t="s">
+        <v>41</v>
+      </c>
+      <c r="N12" s="31"/>
+      <c r="O12" s="32"/>
+      <c r="P12" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="Q12" s="44" t="s">
         <v>59</v>
       </c>
-      <c r="H12" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="J12" s="58"/>
-      <c r="K12" s="28" t="s">
-        <v>39</v>
-      </c>
-      <c r="L12" s="21" t="s">
-        <v>67</v>
-      </c>
-      <c r="M12" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="N12" s="38"/>
-      <c r="O12" s="39"/>
-      <c r="P12" s="21" t="s">
+      <c r="S12" s="53"/>
+      <c r="T12" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="U12" s="41" t="s">
         <v>46</v>
       </c>
-      <c r="Q12" s="29" t="s">
-        <v>65</v>
-      </c>
-      <c r="S12" s="58"/>
-      <c r="T12" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="U12" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="V12" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="W12" s="38"/>
-      <c r="X12" s="39"/>
-      <c r="Y12" s="22"/>
-      <c r="Z12" s="18"/>
-      <c r="AA12" s="58"/>
-      <c r="AB12" s="21" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC12" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD12" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="AE12" s="38"/>
-      <c r="AF12" s="39"/>
-      <c r="AG12" s="25"/>
+      <c r="V12" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="W12" s="31"/>
+      <c r="X12" s="32"/>
+      <c r="Y12" s="20"/>
+      <c r="Z12" s="16"/>
+      <c r="AA12" s="53"/>
+      <c r="AB12" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC12" s="22" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD12" s="22" t="s">
+        <v>27</v>
+      </c>
+      <c r="AE12" s="31"/>
+      <c r="AF12" s="32"/>
+      <c r="AG12" s="23"/>
     </row>
     <row r="13" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="Z13" s="14"/>
+      <c r="G13" s="34"/>
+      <c r="Z13" s="12"/>
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A14" s="47" t="s">
-        <v>78</v>
-      </c>
-      <c r="B14" s="47"/>
-      <c r="C14" s="47"/>
-      <c r="D14" s="47"/>
-      <c r="E14" s="47"/>
-      <c r="F14" s="47"/>
-      <c r="G14" s="47"/>
-      <c r="H14" s="47"/>
-      <c r="Z14" s="14"/>
-      <c r="AF14" s="13"/>
-      <c r="AG14" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="AH14" s="13"/>
+      <c r="A14" s="69"/>
+      <c r="B14" s="69"/>
+      <c r="C14" s="69"/>
+      <c r="D14" s="69"/>
+      <c r="E14" s="69"/>
+      <c r="F14" s="69"/>
+      <c r="G14" s="69"/>
+      <c r="H14" s="69"/>
+      <c r="J14" s="68" t="s">
+        <v>69</v>
+      </c>
+      <c r="K14" s="68" t="s">
+        <v>70</v>
+      </c>
+      <c r="L14" s="12"/>
+      <c r="M14" s="12"/>
+      <c r="N14" s="12"/>
+      <c r="O14" s="12"/>
+      <c r="P14" s="12"/>
+      <c r="Z14" s="12"/>
+      <c r="AF14" s="35"/>
+      <c r="AG14" s="35"/>
+      <c r="AH14" s="35"/>
     </row>
     <row r="15" spans="1:34" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="B15" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>28</v>
-      </c>
-      <c r="K15" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="L15" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="M15" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="N15" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="Z15" s="14"/>
-      <c r="AF15" s="13"/>
-      <c r="AG15" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="AH15" s="13" t="s">
-        <v>76</v>
-      </c>
+      <c r="A15" s="12"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="12"/>
+      <c r="D15" s="12"/>
+      <c r="E15" s="12"/>
+      <c r="F15" s="12"/>
+      <c r="G15" s="12"/>
+      <c r="H15" s="12"/>
+      <c r="J15" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="K15" s="11">
+        <v>15</v>
+      </c>
+      <c r="L15" s="12"/>
+      <c r="M15" s="12"/>
+      <c r="N15" s="12"/>
+      <c r="O15" s="12"/>
+      <c r="P15" s="12"/>
+      <c r="S15" s="12"/>
+      <c r="T15" s="12"/>
+      <c r="U15" s="12"/>
+      <c r="V15" s="12"/>
+      <c r="W15" s="12"/>
+      <c r="X15" s="12"/>
+      <c r="Y15" s="12"/>
+      <c r="Z15" s="12"/>
+      <c r="AA15" s="12"/>
+      <c r="AB15" s="12"/>
+      <c r="AC15" s="12"/>
+      <c r="AD15" s="12"/>
+      <c r="AE15" s="12"/>
+      <c r="AF15" s="35"/>
+      <c r="AG15" s="35"/>
+      <c r="AH15" s="35"/>
     </row>
     <row r="16" spans="1:34" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="40" t="s">
-        <v>53</v>
-      </c>
-      <c r="C16" s="41" t="s">
-        <v>31</v>
-      </c>
-      <c r="D16" s="42" t="s">
-        <v>54</v>
-      </c>
-      <c r="E16" s="44" t="s">
+      <c r="A16" s="12"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="12"/>
+      <c r="E16" s="12"/>
+      <c r="F16" s="12"/>
+      <c r="G16" s="12"/>
+      <c r="H16" s="12"/>
+      <c r="J16" s="11" t="s">
         <v>56</v>
       </c>
-      <c r="K16" s="41" t="s">
-        <v>39</v>
-      </c>
-      <c r="L16" s="40" t="s">
-        <v>60</v>
-      </c>
-      <c r="M16" s="42" t="s">
-        <v>40</v>
-      </c>
-      <c r="N16" s="44" t="s">
-        <v>42</v>
-      </c>
-      <c r="S16" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="T16" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="U16" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="V16" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="AA16" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="AB16" s="13" t="s">
-        <v>9</v>
-      </c>
-      <c r="AC16" s="13" t="s">
-        <v>10</v>
-      </c>
-      <c r="AD16" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="AF16" s="13">
-        <v>1</v>
-      </c>
-      <c r="AG16" s="13">
-        <v>1</v>
-      </c>
-      <c r="AH16" s="13">
-        <v>1</v>
-      </c>
+      <c r="K16" s="11">
+        <v>15</v>
+      </c>
+      <c r="L16" s="12"/>
+      <c r="M16" s="12"/>
+      <c r="N16" s="12"/>
+      <c r="O16" s="12"/>
+      <c r="P16" s="12"/>
+      <c r="S16" s="12"/>
+      <c r="T16" s="12"/>
+      <c r="U16" s="12"/>
+      <c r="V16" s="12"/>
+      <c r="W16" s="12"/>
+      <c r="X16" s="12"/>
+      <c r="Y16" s="12"/>
+      <c r="Z16" s="12"/>
+      <c r="AA16" s="12"/>
+      <c r="AB16" s="12"/>
+      <c r="AC16" s="12"/>
+      <c r="AD16" s="12"/>
+      <c r="AE16" s="12"/>
+      <c r="AF16" s="35"/>
+      <c r="AG16" s="35"/>
+      <c r="AH16" s="35"/>
     </row>
-    <row r="17" spans="2:34" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="32" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" s="34" t="s">
-        <v>32</v>
-      </c>
-      <c r="E17" s="44" t="s">
-        <v>36</v>
-      </c>
-      <c r="K17" s="32" t="s">
-        <v>67</v>
-      </c>
-      <c r="M17" s="42" t="s">
-        <v>62</v>
-      </c>
-      <c r="N17" s="44" t="s">
-        <v>64</v>
-      </c>
-      <c r="T17" s="40" t="s">
-        <v>50</v>
-      </c>
-      <c r="U17" s="41" t="s">
-        <v>68</v>
-      </c>
-      <c r="V17" s="43" t="s">
-        <v>69</v>
-      </c>
-      <c r="Z17" s="11"/>
-      <c r="AB17" s="40" t="s">
-        <v>48</v>
-      </c>
-      <c r="AC17" s="40" t="s">
-        <v>72</v>
-      </c>
-      <c r="AD17" s="42" t="s">
-        <v>45</v>
-      </c>
-      <c r="AF17" s="13">
-        <v>2</v>
-      </c>
-      <c r="AG17" s="13">
-        <v>1</v>
-      </c>
-      <c r="AH17" s="13">
-        <v>1</v>
-      </c>
+    <row r="17" spans="1:34" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="12"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="12"/>
+      <c r="G17" s="12"/>
+      <c r="H17" s="12"/>
+      <c r="J17" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="K17" s="11">
+        <v>14</v>
+      </c>
+      <c r="L17" s="12"/>
+      <c r="M17" s="12"/>
+      <c r="N17" s="12"/>
+      <c r="O17" s="12"/>
+      <c r="P17" s="12"/>
+      <c r="S17" s="12"/>
+      <c r="T17" s="12"/>
+      <c r="U17" s="12"/>
+      <c r="V17" s="12"/>
+      <c r="W17" s="12"/>
+      <c r="X17" s="12"/>
+      <c r="Y17" s="12"/>
+      <c r="Z17" s="12"/>
+      <c r="AA17" s="12"/>
+      <c r="AB17" s="12"/>
+      <c r="AC17" s="12"/>
+      <c r="AD17" s="12"/>
+      <c r="AE17" s="12"/>
+      <c r="AF17" s="35"/>
+      <c r="AG17" s="35"/>
+      <c r="AH17" s="35"/>
     </row>
-    <row r="18" spans="2:34" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D18" s="42" t="s">
-        <v>35</v>
-      </c>
-      <c r="E18" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="M18" s="42" t="s">
-        <v>41</v>
-      </c>
-      <c r="N18" s="44" t="s">
-        <v>44</v>
-      </c>
-      <c r="T18" s="32" t="s">
-        <v>43</v>
-      </c>
-      <c r="V18" s="43" t="s">
-        <v>47</v>
-      </c>
-      <c r="Z18" s="11"/>
-      <c r="AB18" s="32" t="s">
-        <v>70</v>
-      </c>
-      <c r="AD18" s="42" t="s">
-        <v>73</v>
-      </c>
-      <c r="AF18" s="13">
-        <v>3</v>
-      </c>
-      <c r="AG18" s="13">
-        <v>1</v>
-      </c>
-      <c r="AH18" s="13">
-        <v>1</v>
-      </c>
+    <row r="18" spans="1:34" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="12"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="12"/>
+      <c r="P18" s="12"/>
+      <c r="S18" s="12"/>
+      <c r="T18" s="12"/>
+      <c r="U18" s="12"/>
+      <c r="V18" s="12"/>
+      <c r="W18" s="12"/>
+      <c r="X18" s="12"/>
+      <c r="Y18" s="12"/>
+      <c r="Z18" s="12"/>
+      <c r="AA18" s="12"/>
+      <c r="AB18" s="12"/>
+      <c r="AC18" s="12"/>
+      <c r="AD18" s="12"/>
+      <c r="AE18" s="12"/>
+      <c r="AF18" s="35"/>
+      <c r="AG18" s="35"/>
+      <c r="AH18" s="35"/>
     </row>
-    <row r="19" spans="2:34" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D19" s="32" t="s">
-        <v>57</v>
-      </c>
-      <c r="E19" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="M19" s="42" t="s">
-        <v>61</v>
-      </c>
-      <c r="N19" s="40" t="s">
-        <v>51</v>
-      </c>
-      <c r="V19" s="43" t="s">
-        <v>71</v>
-      </c>
-      <c r="Z19" s="11"/>
-      <c r="AD19" s="42" t="s">
-        <v>75</v>
-      </c>
-      <c r="AF19" s="13">
-        <v>4</v>
-      </c>
-      <c r="AG19" s="13"/>
-      <c r="AH19" s="13">
-        <v>1</v>
-      </c>
+    <row r="19" spans="1:34" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="12"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="12"/>
+      <c r="N19" s="12"/>
+      <c r="O19" s="12"/>
+      <c r="P19" s="12"/>
+      <c r="S19" s="12"/>
+      <c r="T19" s="12"/>
+      <c r="U19" s="12"/>
+      <c r="V19" s="12"/>
+      <c r="W19" s="12"/>
+      <c r="X19" s="12"/>
+      <c r="Y19" s="12"/>
+      <c r="Z19" s="12"/>
+      <c r="AA19" s="12"/>
+      <c r="AB19" s="12"/>
+      <c r="AC19" s="12"/>
+      <c r="AD19" s="12"/>
+      <c r="AE19" s="12"/>
+      <c r="AF19" s="35"/>
+      <c r="AG19" s="35"/>
+      <c r="AH19" s="35"/>
     </row>
-    <row r="20" spans="2:34" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E20" s="44" t="s">
-        <v>38</v>
-      </c>
-      <c r="N20" s="44" t="s">
-        <v>63</v>
-      </c>
-      <c r="V20" s="43" t="s">
-        <v>52</v>
-      </c>
-      <c r="Z20" s="11"/>
-      <c r="AD20" s="46" t="s">
-        <v>74</v>
-      </c>
-      <c r="AF20" s="13">
-        <v>5</v>
-      </c>
-      <c r="AG20" s="13">
-        <v>1</v>
-      </c>
-      <c r="AH20" s="13">
-        <v>1</v>
-      </c>
+    <row r="20" spans="1:34" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="12"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
+      <c r="O20" s="12"/>
+      <c r="P20" s="12"/>
+      <c r="S20" s="12"/>
+      <c r="T20" s="12"/>
+      <c r="U20" s="12"/>
+      <c r="V20" s="12"/>
+      <c r="W20" s="12"/>
+      <c r="X20" s="12"/>
+      <c r="Y20" s="12"/>
+      <c r="Z20" s="12"/>
+      <c r="AA20" s="12"/>
+      <c r="AB20" s="12"/>
+      <c r="AC20" s="12"/>
+      <c r="AD20" s="12"/>
+      <c r="AE20" s="12"/>
+      <c r="AF20" s="35"/>
+      <c r="AG20" s="35"/>
+      <c r="AH20" s="35"/>
     </row>
-    <row r="21" spans="2:34" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E21" s="40" t="s">
-        <v>58</v>
-      </c>
-      <c r="N21" s="40" t="s">
-        <v>66</v>
-      </c>
-      <c r="Z21" s="11"/>
-      <c r="AF21" s="13">
-        <v>6</v>
-      </c>
-      <c r="AG21" s="13">
-        <v>1</v>
-      </c>
-      <c r="AH21" s="13">
-        <v>1</v>
-      </c>
+    <row r="21" spans="1:34" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="12"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="12"/>
+      <c r="O21" s="12"/>
+      <c r="P21" s="12"/>
+      <c r="S21" s="12"/>
+      <c r="T21" s="12"/>
+      <c r="U21" s="12"/>
+      <c r="V21" s="12"/>
+      <c r="W21" s="12"/>
+      <c r="X21" s="12"/>
+      <c r="Y21" s="12"/>
+      <c r="Z21" s="12"/>
+      <c r="AA21" s="12"/>
+      <c r="AB21" s="12"/>
+      <c r="AC21" s="12"/>
+      <c r="AD21" s="12"/>
+      <c r="AE21" s="12"/>
+      <c r="AF21" s="35"/>
+      <c r="AG21" s="35"/>
+      <c r="AH21" s="35"/>
     </row>
-    <row r="22" spans="2:34" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E22" s="44" t="s">
-        <v>59</v>
-      </c>
-      <c r="N22" s="44" t="s">
-        <v>46</v>
-      </c>
-      <c r="AF22" s="13">
-        <v>7</v>
-      </c>
-      <c r="AG22" s="13">
-        <v>1</v>
-      </c>
-      <c r="AH22" s="13"/>
+    <row r="22" spans="1:34" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="12"/>
+      <c r="B22" s="12"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
+      <c r="L22" s="12"/>
+      <c r="M22" s="12"/>
+      <c r="N22" s="12"/>
+      <c r="O22" s="12"/>
+      <c r="P22" s="12"/>
+      <c r="AF22" s="35"/>
+      <c r="AG22" s="35"/>
+      <c r="AH22" s="35"/>
     </row>
-    <row r="23" spans="2:34" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E23" s="40" t="s">
-        <v>33</v>
-      </c>
-      <c r="N23" s="40" t="s">
-        <v>65</v>
-      </c>
+    <row r="23" spans="1:34" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="12"/>
+      <c r="B23" s="12"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="12"/>
+      <c r="M23" s="12"/>
+      <c r="N23" s="12"/>
+      <c r="O23" s="12"/>
+      <c r="P23" s="12"/>
     </row>
-    <row r="24" spans="2:34" ht="20.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="25" spans="2:34" ht="20.25" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="1:34" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="12"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="12"/>
+      <c r="O24" s="12"/>
+      <c r="P24" s="12"/>
+    </row>
+    <row r="25" spans="1:34" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="12"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+    </row>
+    <row r="26" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A26" s="12"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+    </row>
+    <row r="27" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A27" s="12"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+    </row>
+    <row r="28" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A28" s="12"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+    </row>
+    <row r="29" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A29" s="12"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+    </row>
+    <row r="30" spans="1:34" x14ac:dyDescent="0.3">
+      <c r="A30" s="12"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+    </row>
   </sheetData>
   <mergeCells count="103">
     <mergeCell ref="A1:C1"/>
@@ -2485,6 +3172,12 @@
     <mergeCell ref="G2:H2"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="C3:C4"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="B7:B8"/>
+    <mergeCell ref="L3:L4"/>
+    <mergeCell ref="M3:M4"/>
     <mergeCell ref="AA1:AC1"/>
     <mergeCell ref="AE2:AF2"/>
     <mergeCell ref="AA3:AA4"/>
@@ -2500,19 +3193,15 @@
     <mergeCell ref="S3:S4"/>
     <mergeCell ref="V3:V4"/>
     <mergeCell ref="S5:S6"/>
-    <mergeCell ref="B2:C2"/>
     <mergeCell ref="AB2:AC2"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="B7:B8"/>
     <mergeCell ref="AA5:AA6"/>
     <mergeCell ref="AC5:AC6"/>
     <mergeCell ref="AA7:AA8"/>
     <mergeCell ref="AC7:AC8"/>
     <mergeCell ref="AB5:AB6"/>
     <mergeCell ref="AB7:AB8"/>
-    <mergeCell ref="L3:L4"/>
-    <mergeCell ref="M3:M4"/>
+    <mergeCell ref="U9:U10"/>
+    <mergeCell ref="T9:T10"/>
     <mergeCell ref="J5:J6"/>
     <mergeCell ref="L5:L6"/>
     <mergeCell ref="M5:M6"/>
@@ -2524,12 +3213,9 @@
     <mergeCell ref="U3:U4"/>
     <mergeCell ref="U5:U6"/>
     <mergeCell ref="U7:U8"/>
-    <mergeCell ref="U9:U10"/>
     <mergeCell ref="T3:T4"/>
     <mergeCell ref="T5:T6"/>
     <mergeCell ref="T7:T8"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="L9:L10"/>
     <mergeCell ref="M9:M10"/>
     <mergeCell ref="AF3:AF4"/>
     <mergeCell ref="AF5:AF6"/>
@@ -2570,9 +3256,10 @@
     <mergeCell ref="AA11:AA12"/>
     <mergeCell ref="S11:S12"/>
     <mergeCell ref="J11:J12"/>
+    <mergeCell ref="L9:L10"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="0" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/4학년피구대회일정.xlsx
+++ b/4학년피구대회일정.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\2026\학년협의\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\2026 송명신\피구대회\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31B9403C-0192-4F07-80F6-1A3C717B1369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D512ADB-222F-4DA8-B7E9-711B6DB937D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="420" yWindow="0" windowWidth="28215" windowHeight="15480" xr2:uid="{DD21F046-BAC6-4B5D-AC41-BB8291C46378}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{DD21F046-BAC6-4B5D-AC41-BB8291C46378}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -521,7 +521,7 @@
   </si>
   <si>
     <r>
-      <t>6반:</t>
+      <t>7반</t>
     </r>
     <r>
       <rPr>
@@ -532,506 +532,525 @@
         <charset val="129"/>
         <scheme val="minor"/>
       </rPr>
+      <t>:4반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>14반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:1반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>12반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:13반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>7반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:11반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>14반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:13반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2위:2위</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>1위:1위</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>13반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:9반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>14반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:12반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>3반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>4반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:10반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이순희</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>11반:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>1반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:12반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10반:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>11반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:7반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>8반:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>13반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2반:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>11반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>1반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:9반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>14반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:6반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>2반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:4반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:10반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>14반:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>8반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>2반:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>심판명</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>횟수</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>3반:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>10반</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>6반</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </rPr>
       <t>9반</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>7반</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:4반</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>14반</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:1반</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>12반</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:13반</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>7반</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:11반</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>14반</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:13반</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>2위:2위</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>1위:1위</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>13반</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:9반</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>14반</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:12반</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2반</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>3반</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>4반</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:10반</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>이순희</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>11반:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>5반</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>1반</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:12반</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>10반:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>11반</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>5반</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:7반</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>8반:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>13반</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>2반:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>11반</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>1반</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:9반</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>14반</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:6반</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>2반</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:4반</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>5반</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>:10반</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>14반:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>8반</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>2반:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>10반</t>
-    </r>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>심판명</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>횟수</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>3반:</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFFF0000"/>
-        <rFont val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>10반</t>
     </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1688,6 +1707,63 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1697,65 +1773,8 @@
     <xf numFmtId="0" fontId="10" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2111,81 +2130,81 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="B1" s="59"/>
-      <c r="C1" s="59"/>
+      <c r="B1" s="50"/>
+      <c r="C1" s="50"/>
       <c r="D1" s="9"/>
-      <c r="J1" s="59" t="s">
+      <c r="J1" s="50" t="s">
         <v>15</v>
       </c>
-      <c r="K1" s="59"/>
-      <c r="L1" s="59"/>
-      <c r="S1" s="59" t="s">
+      <c r="K1" s="50"/>
+      <c r="L1" s="50"/>
+      <c r="S1" s="50" t="s">
         <v>16</v>
       </c>
-      <c r="T1" s="59"/>
-      <c r="U1" s="59"/>
+      <c r="T1" s="50"/>
+      <c r="U1" s="50"/>
       <c r="Z1" s="12"/>
-      <c r="AA1" s="59" t="s">
+      <c r="AA1" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="AB1" s="59"/>
-      <c r="AC1" s="59"/>
+      <c r="AB1" s="50"/>
+      <c r="AC1" s="50"/>
       <c r="AD1" s="9"/>
     </row>
     <row r="2" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="57" t="s">
+      <c r="B2" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="58"/>
+      <c r="C2" s="60"/>
       <c r="D2" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="60" t="s">
+      <c r="E2" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="61"/>
-      <c r="G2" s="60" t="s">
+      <c r="F2" s="52"/>
+      <c r="G2" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="64"/>
+      <c r="H2" s="53"/>
       <c r="J2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="K2" s="57" t="s">
+      <c r="K2" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="L2" s="58"/>
+      <c r="L2" s="60"/>
       <c r="M2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="N2" s="60" t="s">
+      <c r="N2" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="O2" s="61"/>
-      <c r="P2" s="60" t="s">
+      <c r="O2" s="52"/>
+      <c r="P2" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="Q2" s="64"/>
+      <c r="Q2" s="53"/>
       <c r="S2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="T2" s="57" t="s">
+      <c r="T2" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="U2" s="58"/>
+      <c r="U2" s="60"/>
       <c r="V2" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="W2" s="60" t="s">
+      <c r="W2" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="X2" s="61"/>
+      <c r="X2" s="52"/>
       <c r="Y2" s="26" t="s">
         <v>2</v>
       </c>
@@ -2193,28 +2212,28 @@
       <c r="AA2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="AB2" s="57" t="s">
+      <c r="AB2" s="59" t="s">
         <v>8</v>
       </c>
-      <c r="AC2" s="58"/>
+      <c r="AC2" s="60"/>
       <c r="AD2" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AE2" s="60" t="s">
+      <c r="AE2" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="AF2" s="61"/>
+      <c r="AF2" s="52"/>
       <c r="AG2" s="27" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:34" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="55" t="s">
+      <c r="A3" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="50"/>
-      <c r="C3" s="50"/>
-      <c r="D3" s="50"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
       <c r="E3" s="1" t="s">
         <v>10</v>
       </c>
@@ -2224,54 +2243,54 @@
       <c r="G3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="51"/>
-      <c r="J3" s="55" t="s">
+      <c r="H3" s="64"/>
+      <c r="J3" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="K3" s="50"/>
-      <c r="L3" s="50"/>
-      <c r="M3" s="54"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="58"/>
+      <c r="M3" s="61"/>
       <c r="N3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O3" s="50"/>
+      <c r="O3" s="58"/>
       <c r="P3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="Q3" s="51"/>
-      <c r="S3" s="55" t="s">
+      <c r="Q3" s="64"/>
+      <c r="S3" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="T3" s="50"/>
-      <c r="U3" s="50"/>
+      <c r="T3" s="58"/>
+      <c r="U3" s="58"/>
       <c r="V3" s="62"/>
       <c r="W3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="X3" s="50"/>
+      <c r="X3" s="58"/>
       <c r="Y3" s="7" t="s">
         <v>17</v>
       </c>
       <c r="Z3" s="14"/>
-      <c r="AA3" s="55" t="s">
+      <c r="AA3" s="54" t="s">
         <v>4</v>
       </c>
-      <c r="AB3" s="50"/>
-      <c r="AC3" s="50"/>
-      <c r="AD3" s="50"/>
-      <c r="AE3" s="66" t="s">
+      <c r="AB3" s="58"/>
+      <c r="AC3" s="58"/>
+      <c r="AD3" s="58"/>
+      <c r="AE3" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="AF3" s="50"/>
+      <c r="AF3" s="58"/>
       <c r="AG3" s="5" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:34" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="56"/>
-      <c r="B4" s="50"/>
-      <c r="C4" s="50"/>
-      <c r="D4" s="50"/>
+      <c r="A4" s="55"/>
+      <c r="B4" s="58"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
       <c r="E4" s="42" t="s">
         <v>35</v>
       </c>
@@ -2279,50 +2298,50 @@
         <v>36</v>
       </c>
       <c r="G4" s="43" t="s">
-        <v>52</v>
-      </c>
-      <c r="H4" s="51"/>
-      <c r="J4" s="56"/>
-      <c r="K4" s="50"/>
-      <c r="L4" s="50"/>
-      <c r="M4" s="54"/>
+        <v>51</v>
+      </c>
+      <c r="H4" s="64"/>
+      <c r="J4" s="55"/>
+      <c r="K4" s="58"/>
+      <c r="L4" s="58"/>
+      <c r="M4" s="61"/>
       <c r="N4" s="42" t="s">
-        <v>55</v>
-      </c>
-      <c r="O4" s="50"/>
+        <v>54</v>
+      </c>
+      <c r="O4" s="58"/>
       <c r="P4" s="43" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q4" s="51"/>
-      <c r="S4" s="56"/>
-      <c r="T4" s="50"/>
-      <c r="U4" s="50"/>
+        <v>64</v>
+      </c>
+      <c r="Q4" s="64"/>
+      <c r="S4" s="55"/>
+      <c r="T4" s="58"/>
+      <c r="U4" s="58"/>
       <c r="V4" s="63"/>
       <c r="W4" s="43" t="s">
-        <v>47</v>
-      </c>
-      <c r="X4" s="50"/>
+        <v>46</v>
+      </c>
+      <c r="X4" s="58"/>
       <c r="Y4" s="7" t="s">
         <v>18</v>
       </c>
       <c r="Z4" s="14"/>
-      <c r="AA4" s="56"/>
-      <c r="AB4" s="50"/>
-      <c r="AC4" s="50"/>
-      <c r="AD4" s="50"/>
+      <c r="AA4" s="55"/>
+      <c r="AB4" s="58"/>
+      <c r="AC4" s="58"/>
+      <c r="AD4" s="58"/>
       <c r="AE4" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="AF4" s="50"/>
+        <v>67</v>
+      </c>
+      <c r="AF4" s="58"/>
       <c r="AG4" s="6"/>
     </row>
     <row r="5" spans="1:34" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="55" t="s">
+      <c r="A5" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="50"/>
-      <c r="C5" s="50"/>
-      <c r="D5" s="50"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
       <c r="E5" s="1" t="s">
         <v>11</v>
       </c>
@@ -2332,50 +2351,50 @@
       <c r="G5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="H5" s="51"/>
-      <c r="J5" s="55" t="s">
+      <c r="H5" s="64"/>
+      <c r="J5" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="K5" s="50"/>
-      <c r="L5" s="50"/>
-      <c r="M5" s="54"/>
+      <c r="K5" s="58"/>
+      <c r="L5" s="58"/>
+      <c r="M5" s="61"/>
       <c r="N5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="O5" s="50"/>
+      <c r="O5" s="58"/>
       <c r="P5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="Q5" s="51"/>
-      <c r="S5" s="55" t="s">
+      <c r="Q5" s="64"/>
+      <c r="S5" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="T5" s="50"/>
-      <c r="U5" s="50"/>
+      <c r="T5" s="58"/>
+      <c r="U5" s="58"/>
       <c r="V5" s="62"/>
       <c r="W5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="X5" s="50"/>
+      <c r="X5" s="58"/>
       <c r="Y5" s="7"/>
       <c r="Z5" s="14"/>
-      <c r="AA5" s="55" t="s">
+      <c r="AA5" s="54" t="s">
         <v>5</v>
       </c>
-      <c r="AB5" s="50"/>
-      <c r="AC5" s="50"/>
-      <c r="AD5" s="50"/>
+      <c r="AB5" s="58"/>
+      <c r="AC5" s="58"/>
+      <c r="AD5" s="58"/>
       <c r="AE5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="AF5" s="50"/>
+      <c r="AF5" s="58"/>
       <c r="AG5" s="5"/>
     </row>
     <row r="6" spans="1:34" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="56"/>
-      <c r="B6" s="50"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
+      <c r="A6" s="55"/>
+      <c r="B6" s="58"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
       <c r="E6" s="10" t="s">
         <v>32</v>
       </c>
@@ -2383,253 +2402,253 @@
         <v>37</v>
       </c>
       <c r="G6" s="46" t="s">
-        <v>53</v>
-      </c>
-      <c r="H6" s="51"/>
-      <c r="J6" s="56"/>
-      <c r="K6" s="50"/>
-      <c r="L6" s="50"/>
-      <c r="M6" s="54"/>
+        <v>52</v>
+      </c>
+      <c r="H6" s="64"/>
+      <c r="J6" s="55"/>
+      <c r="K6" s="58"/>
+      <c r="L6" s="58"/>
+      <c r="M6" s="61"/>
       <c r="N6" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="O6" s="50"/>
+      <c r="O6" s="58"/>
       <c r="P6" s="43" t="s">
-        <v>64</v>
-      </c>
-      <c r="Q6" s="51"/>
-      <c r="S6" s="56"/>
-      <c r="T6" s="50"/>
-      <c r="U6" s="50"/>
+        <v>63</v>
+      </c>
+      <c r="Q6" s="64"/>
+      <c r="S6" s="55"/>
+      <c r="T6" s="58"/>
+      <c r="U6" s="58"/>
       <c r="V6" s="63"/>
       <c r="W6" s="43" t="s">
-        <v>57</v>
-      </c>
-      <c r="X6" s="50"/>
+        <v>56</v>
+      </c>
+      <c r="X6" s="58"/>
       <c r="Y6" s="8"/>
       <c r="Z6" s="14"/>
-      <c r="AA6" s="56"/>
-      <c r="AB6" s="50"/>
-      <c r="AC6" s="50"/>
-      <c r="AD6" s="50"/>
+      <c r="AA6" s="55"/>
+      <c r="AB6" s="58"/>
+      <c r="AC6" s="58"/>
+      <c r="AD6" s="58"/>
       <c r="AE6" s="43" t="s">
-        <v>49</v>
-      </c>
-      <c r="AF6" s="50"/>
+        <v>48</v>
+      </c>
+      <c r="AF6" s="58"/>
       <c r="AG6" s="6"/>
     </row>
     <row r="7" spans="1:34" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="55" t="s">
+      <c r="A7" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="50"/>
-      <c r="C7" s="50"/>
-      <c r="D7" s="50"/>
-      <c r="E7" s="47" t="s">
+      <c r="B7" s="58"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="48"/>
+      <c r="F7" s="67"/>
       <c r="G7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H7" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="J7" s="55" t="s">
+      <c r="J7" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="K7" s="50"/>
-      <c r="L7" s="50"/>
-      <c r="M7" s="54"/>
+      <c r="K7" s="58"/>
+      <c r="L7" s="58"/>
+      <c r="M7" s="61"/>
       <c r="N7" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="O7" s="50"/>
+      <c r="O7" s="58"/>
       <c r="P7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="Q7" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="S7" s="55" t="s">
+      <c r="S7" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="T7" s="50"/>
-      <c r="U7" s="50"/>
+      <c r="T7" s="58"/>
+      <c r="U7" s="58"/>
       <c r="V7" s="62"/>
       <c r="W7" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="X7" s="50"/>
+      <c r="X7" s="58"/>
       <c r="Y7" s="7"/>
       <c r="Z7" s="15"/>
-      <c r="AA7" s="55" t="s">
+      <c r="AA7" s="54" t="s">
         <v>6</v>
       </c>
-      <c r="AB7" s="50"/>
-      <c r="AC7" s="50"/>
-      <c r="AD7" s="50"/>
+      <c r="AB7" s="58"/>
+      <c r="AC7" s="58"/>
+      <c r="AD7" s="58"/>
       <c r="AE7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="AF7" s="50"/>
+      <c r="AF7" s="58"/>
       <c r="AG7" s="5"/>
     </row>
     <row r="8" spans="1:34" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="56"/>
-      <c r="B8" s="50"/>
-      <c r="C8" s="50"/>
-      <c r="D8" s="50"/>
-      <c r="E8" s="47" t="s">
+      <c r="A8" s="55"/>
+      <c r="B8" s="58"/>
+      <c r="C8" s="58"/>
+      <c r="D8" s="58"/>
+      <c r="E8" s="66" t="s">
         <v>30</v>
       </c>
-      <c r="F8" s="48"/>
+      <c r="F8" s="67"/>
       <c r="G8" s="28" t="s">
         <v>38</v>
       </c>
       <c r="H8" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="J8" s="56"/>
-      <c r="K8" s="50"/>
-      <c r="L8" s="50"/>
-      <c r="M8" s="54"/>
+      <c r="J8" s="55"/>
+      <c r="K8" s="58"/>
+      <c r="L8" s="58"/>
+      <c r="M8" s="61"/>
       <c r="N8" s="42" t="s">
-        <v>60</v>
-      </c>
-      <c r="O8" s="50"/>
+        <v>59</v>
+      </c>
+      <c r="O8" s="58"/>
       <c r="P8" s="43" t="s">
         <v>43</v>
       </c>
-      <c r="Q8" s="11" t="s">
-        <v>44</v>
-      </c>
-      <c r="S8" s="56"/>
-      <c r="T8" s="50"/>
-      <c r="U8" s="50"/>
+      <c r="Q8" s="43" t="s">
+        <v>71</v>
+      </c>
+      <c r="S8" s="55"/>
+      <c r="T8" s="58"/>
+      <c r="U8" s="58"/>
       <c r="V8" s="63"/>
       <c r="W8" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="X8" s="50"/>
+      <c r="X8" s="58"/>
       <c r="Y8" s="8"/>
       <c r="Z8" s="16"/>
-      <c r="AA8" s="56"/>
-      <c r="AB8" s="50"/>
-      <c r="AC8" s="50"/>
-      <c r="AD8" s="50"/>
+      <c r="AA8" s="55"/>
+      <c r="AB8" s="58"/>
+      <c r="AC8" s="58"/>
+      <c r="AD8" s="58"/>
       <c r="AE8" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="AF8" s="50"/>
+        <v>49</v>
+      </c>
+      <c r="AF8" s="58"/>
       <c r="AG8" s="6"/>
     </row>
     <row r="9" spans="1:34" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="55" t="s">
+      <c r="A9" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="50"/>
-      <c r="C9" s="50"/>
-      <c r="D9" s="50"/>
-      <c r="E9" s="47" t="s">
+      <c r="B9" s="58"/>
+      <c r="C9" s="58"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="66" t="s">
         <v>21</v>
       </c>
-      <c r="F9" s="48"/>
+      <c r="F9" s="67"/>
       <c r="G9" s="2" t="s">
         <v>12</v>
       </c>
       <c r="H9" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="J9" s="55" t="s">
+      <c r="J9" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="K9" s="50"/>
-      <c r="L9" s="50"/>
-      <c r="M9" s="54"/>
-      <c r="N9" s="66" t="s">
+      <c r="K9" s="58"/>
+      <c r="L9" s="58"/>
+      <c r="M9" s="61"/>
+      <c r="N9" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="O9" s="50"/>
+      <c r="O9" s="58"/>
       <c r="P9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="Q9" s="67" t="s">
+      <c r="Q9" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="S9" s="55" t="s">
+      <c r="S9" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="T9" s="50"/>
-      <c r="U9" s="50"/>
+      <c r="T9" s="58"/>
+      <c r="U9" s="58"/>
       <c r="V9" s="62"/>
       <c r="W9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="X9" s="50"/>
+      <c r="X9" s="58"/>
       <c r="Y9" s="7"/>
       <c r="Z9" s="15"/>
-      <c r="AA9" s="55" t="s">
+      <c r="AA9" s="54" t="s">
         <v>7</v>
       </c>
-      <c r="AB9" s="50"/>
-      <c r="AC9" s="50"/>
-      <c r="AD9" s="50"/>
+      <c r="AB9" s="58"/>
+      <c r="AC9" s="58"/>
+      <c r="AD9" s="58"/>
       <c r="AE9" s="33" t="s">
         <v>12</v>
       </c>
-      <c r="AF9" s="50"/>
+      <c r="AF9" s="58"/>
       <c r="AG9" s="5"/>
     </row>
     <row r="10" spans="1:34" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="56"/>
-      <c r="B10" s="50"/>
-      <c r="C10" s="50"/>
-      <c r="D10" s="50"/>
-      <c r="E10" s="49"/>
-      <c r="F10" s="48"/>
+      <c r="A10" s="55"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="68"/>
+      <c r="F10" s="67"/>
       <c r="G10" s="43" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="H10" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="J10" s="56"/>
-      <c r="K10" s="50"/>
-      <c r="L10" s="50"/>
-      <c r="M10" s="54"/>
+      <c r="J10" s="55"/>
+      <c r="K10" s="58"/>
+      <c r="L10" s="58"/>
+      <c r="M10" s="61"/>
       <c r="N10" s="42" t="s">
-        <v>67</v>
-      </c>
-      <c r="O10" s="50"/>
+        <v>66</v>
+      </c>
+      <c r="O10" s="58"/>
       <c r="P10" s="43" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="Q10" s="45" t="s">
-        <v>61</v>
-      </c>
-      <c r="S10" s="56"/>
-      <c r="T10" s="50"/>
-      <c r="U10" s="50"/>
+        <v>60</v>
+      </c>
+      <c r="S10" s="55"/>
+      <c r="T10" s="58"/>
+      <c r="U10" s="58"/>
       <c r="V10" s="63"/>
       <c r="W10" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="X10" s="50"/>
+        <v>47</v>
+      </c>
+      <c r="X10" s="58"/>
       <c r="Y10" s="8"/>
       <c r="Z10" s="16"/>
-      <c r="AA10" s="56"/>
-      <c r="AB10" s="50"/>
-      <c r="AC10" s="50"/>
-      <c r="AD10" s="50"/>
+      <c r="AA10" s="55"/>
+      <c r="AB10" s="58"/>
+      <c r="AC10" s="58"/>
+      <c r="AD10" s="58"/>
       <c r="AE10" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="AF10" s="50"/>
+        <v>50</v>
+      </c>
+      <c r="AF10" s="58"/>
       <c r="AG10" s="6"/>
     </row>
     <row r="11" spans="1:34" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="65" t="s">
+      <c r="A11" s="56" t="s">
         <v>22</v>
       </c>
       <c r="B11" s="38" t="s">
@@ -2649,14 +2668,14 @@
       <c r="H11" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="J11" s="52" t="s">
+      <c r="J11" s="69" t="s">
         <v>3</v>
       </c>
       <c r="K11" s="37" t="s">
         <v>10</v>
       </c>
       <c r="L11" s="39" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M11" s="39" t="s">
         <v>13</v>
@@ -2669,7 +2688,7 @@
       <c r="Q11" s="40" t="s">
         <v>13</v>
       </c>
-      <c r="S11" s="52" t="s">
+      <c r="S11" s="69" t="s">
         <v>3</v>
       </c>
       <c r="T11" s="39" t="s">
@@ -2685,7 +2704,7 @@
       <c r="X11" s="30"/>
       <c r="Y11" s="7"/>
       <c r="Z11" s="15"/>
-      <c r="AA11" s="52" t="s">
+      <c r="AA11" s="69" t="s">
         <v>3</v>
       </c>
       <c r="AB11" s="39" t="s">
@@ -2702,7 +2721,7 @@
       <c r="AG11" s="5"/>
     </row>
     <row r="12" spans="1:34" ht="35.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="53"/>
+      <c r="A12" s="57"/>
       <c r="B12" s="41" t="s">
         <v>33</v>
       </c>
@@ -2715,17 +2734,17 @@
       <c r="E12" s="31"/>
       <c r="F12" s="32"/>
       <c r="G12" s="41" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="H12" s="44" t="s">
         <v>40</v>
       </c>
-      <c r="J12" s="53"/>
+      <c r="J12" s="57"/>
       <c r="K12" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="L12" s="19" t="s">
         <v>62</v>
-      </c>
-      <c r="L12" s="19" t="s">
-        <v>63</v>
       </c>
       <c r="M12" s="41" t="s">
         <v>41</v>
@@ -2733,26 +2752,26 @@
       <c r="N12" s="31"/>
       <c r="O12" s="32"/>
       <c r="P12" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Q12" s="44" t="s">
-        <v>59</v>
-      </c>
-      <c r="S12" s="53"/>
+        <v>58</v>
+      </c>
+      <c r="S12" s="57"/>
       <c r="T12" s="19" t="s">
         <v>25</v>
       </c>
       <c r="U12" s="41" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="V12" s="19" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="W12" s="31"/>
       <c r="X12" s="32"/>
       <c r="Y12" s="20"/>
       <c r="Z12" s="16"/>
-      <c r="AA12" s="53"/>
+      <c r="AA12" s="57"/>
       <c r="AB12" s="19" t="s">
         <v>24</v>
       </c>
@@ -2771,19 +2790,19 @@
       <c r="Z13" s="12"/>
     </row>
     <row r="14" spans="1:34" x14ac:dyDescent="0.3">
-      <c r="A14" s="69"/>
-      <c r="B14" s="69"/>
-      <c r="C14" s="69"/>
-      <c r="D14" s="69"/>
-      <c r="E14" s="69"/>
-      <c r="F14" s="69"/>
-      <c r="G14" s="69"/>
-      <c r="H14" s="69"/>
-      <c r="J14" s="68" t="s">
+      <c r="A14" s="65"/>
+      <c r="B14" s="65"/>
+      <c r="C14" s="65"/>
+      <c r="D14" s="65"/>
+      <c r="E14" s="65"/>
+      <c r="F14" s="65"/>
+      <c r="G14" s="65"/>
+      <c r="H14" s="65"/>
+      <c r="J14" s="49" t="s">
+        <v>68</v>
+      </c>
+      <c r="K14" s="49" t="s">
         <v>69</v>
-      </c>
-      <c r="K14" s="68" t="s">
-        <v>70</v>
       </c>
       <c r="L14" s="12"/>
       <c r="M14" s="12"/>
@@ -2842,7 +2861,7 @@
       <c r="G16" s="12"/>
       <c r="H16" s="12"/>
       <c r="J16" s="11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="K16" s="11">
         <v>15</v>
@@ -3154,6 +3173,85 @@
     </row>
   </sheetData>
   <mergeCells count="103">
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="AB9:AB10"/>
+    <mergeCell ref="AD3:AD4"/>
+    <mergeCell ref="AD5:AD6"/>
+    <mergeCell ref="AD7:AD8"/>
+    <mergeCell ref="AD9:AD10"/>
+    <mergeCell ref="D3:D4"/>
+    <mergeCell ref="D5:D6"/>
+    <mergeCell ref="D7:D8"/>
+    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="K3:K4"/>
+    <mergeCell ref="K5:K6"/>
+    <mergeCell ref="K7:K8"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="H3:H4"/>
+    <mergeCell ref="H5:H6"/>
+    <mergeCell ref="AA11:AA12"/>
+    <mergeCell ref="S11:S12"/>
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="L9:L10"/>
+    <mergeCell ref="M9:M10"/>
+    <mergeCell ref="AF3:AF4"/>
+    <mergeCell ref="AF5:AF6"/>
+    <mergeCell ref="AF7:AF8"/>
+    <mergeCell ref="AF9:AF10"/>
+    <mergeCell ref="X3:X4"/>
+    <mergeCell ref="X5:X6"/>
+    <mergeCell ref="X7:X8"/>
+    <mergeCell ref="X9:X10"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="O5:O6"/>
+    <mergeCell ref="O7:O8"/>
+    <mergeCell ref="O9:O10"/>
+    <mergeCell ref="Q3:Q4"/>
+    <mergeCell ref="Q5:Q6"/>
+    <mergeCell ref="AA9:AA10"/>
+    <mergeCell ref="AC9:AC10"/>
+    <mergeCell ref="J5:J6"/>
+    <mergeCell ref="L5:L6"/>
+    <mergeCell ref="M5:M6"/>
+    <mergeCell ref="J7:J8"/>
+    <mergeCell ref="L7:L8"/>
+    <mergeCell ref="M7:M8"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="U3:U4"/>
+    <mergeCell ref="U5:U6"/>
+    <mergeCell ref="U7:U8"/>
+    <mergeCell ref="T3:T4"/>
+    <mergeCell ref="T5:T6"/>
+    <mergeCell ref="T7:T8"/>
+    <mergeCell ref="AA1:AC1"/>
+    <mergeCell ref="AE2:AF2"/>
+    <mergeCell ref="AA3:AA4"/>
+    <mergeCell ref="AC3:AC4"/>
+    <mergeCell ref="AB3:AB4"/>
+    <mergeCell ref="V5:V6"/>
+    <mergeCell ref="S7:S8"/>
+    <mergeCell ref="V7:V8"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="V9:V10"/>
+    <mergeCell ref="S1:U1"/>
+    <mergeCell ref="W2:X2"/>
+    <mergeCell ref="S3:S4"/>
+    <mergeCell ref="V3:V4"/>
+    <mergeCell ref="S5:S6"/>
+    <mergeCell ref="AB2:AC2"/>
+    <mergeCell ref="AA5:AA6"/>
+    <mergeCell ref="AC5:AC6"/>
+    <mergeCell ref="AA7:AA8"/>
+    <mergeCell ref="AC7:AC8"/>
+    <mergeCell ref="AB5:AB6"/>
+    <mergeCell ref="AB7:AB8"/>
+    <mergeCell ref="U9:U10"/>
+    <mergeCell ref="T9:T10"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="J1:L1"/>
     <mergeCell ref="N2:O2"/>
@@ -3178,88 +3276,9 @@
     <mergeCell ref="B7:B8"/>
     <mergeCell ref="L3:L4"/>
     <mergeCell ref="M3:M4"/>
-    <mergeCell ref="AA1:AC1"/>
-    <mergeCell ref="AE2:AF2"/>
-    <mergeCell ref="AA3:AA4"/>
-    <mergeCell ref="AC3:AC4"/>
-    <mergeCell ref="AB3:AB4"/>
-    <mergeCell ref="V5:V6"/>
-    <mergeCell ref="S7:S8"/>
-    <mergeCell ref="V7:V8"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="V9:V10"/>
-    <mergeCell ref="S1:U1"/>
-    <mergeCell ref="W2:X2"/>
-    <mergeCell ref="S3:S4"/>
-    <mergeCell ref="V3:V4"/>
-    <mergeCell ref="S5:S6"/>
-    <mergeCell ref="AB2:AC2"/>
-    <mergeCell ref="AA5:AA6"/>
-    <mergeCell ref="AC5:AC6"/>
-    <mergeCell ref="AA7:AA8"/>
-    <mergeCell ref="AC7:AC8"/>
-    <mergeCell ref="AB5:AB6"/>
-    <mergeCell ref="AB7:AB8"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="J5:J6"/>
-    <mergeCell ref="L5:L6"/>
-    <mergeCell ref="M5:M6"/>
-    <mergeCell ref="J7:J8"/>
-    <mergeCell ref="L7:L8"/>
-    <mergeCell ref="M7:M8"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="U3:U4"/>
-    <mergeCell ref="U5:U6"/>
-    <mergeCell ref="U7:U8"/>
-    <mergeCell ref="T3:T4"/>
-    <mergeCell ref="T5:T6"/>
-    <mergeCell ref="T7:T8"/>
-    <mergeCell ref="M9:M10"/>
-    <mergeCell ref="AF3:AF4"/>
-    <mergeCell ref="AF5:AF6"/>
-    <mergeCell ref="AF7:AF8"/>
-    <mergeCell ref="AF9:AF10"/>
-    <mergeCell ref="X3:X4"/>
-    <mergeCell ref="X5:X6"/>
-    <mergeCell ref="X7:X8"/>
-    <mergeCell ref="X9:X10"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="O5:O6"/>
-    <mergeCell ref="O7:O8"/>
-    <mergeCell ref="O9:O10"/>
-    <mergeCell ref="Q3:Q4"/>
-    <mergeCell ref="Q5:Q6"/>
-    <mergeCell ref="AA9:AA10"/>
-    <mergeCell ref="AC9:AC10"/>
-    <mergeCell ref="A14:H14"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="AB9:AB10"/>
-    <mergeCell ref="AD3:AD4"/>
-    <mergeCell ref="AD5:AD6"/>
-    <mergeCell ref="AD7:AD8"/>
-    <mergeCell ref="AD9:AD10"/>
-    <mergeCell ref="D3:D4"/>
-    <mergeCell ref="D5:D6"/>
-    <mergeCell ref="D7:D8"/>
-    <mergeCell ref="D9:D10"/>
-    <mergeCell ref="K3:K4"/>
-    <mergeCell ref="K5:K6"/>
-    <mergeCell ref="K7:K8"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="H3:H4"/>
-    <mergeCell ref="H5:H6"/>
-    <mergeCell ref="AA11:AA12"/>
-    <mergeCell ref="S11:S12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="L9:L10"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="0" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>